--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486316_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486316_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6408</v>
+        <v>3.3049</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4102</v>
+        <v>3.9509</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7694</v>
+        <v>-0.6461</v>
       </c>
       <c r="G2" t="n">
         <v>4.6488</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.3104</v>
+        <v>-1.6463</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.1234</v>
+        <v>-1.5826</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.187</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.2599</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6161</v>
+        <v>2.3477</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6084</v>
+        <v>3.9257</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9923</v>
+        <v>-1.578</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5423</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0586</v>
+        <v>-1.327</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.9179</v>
+        <v>-1.6006</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8593</v>
+        <v>0.2737</v>
       </c>
       <c r="V3" t="n">
         <v>3.5645</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1137</v>
+        <v>1.6223</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0706</v>
+        <v>0.3765</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1842</v>
+        <v>1.2459</v>
       </c>
       <c r="G4" t="n">
         <v>0.6496</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4059</v>
+        <v>0.1027</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3425</v>
+        <v>0.1046</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0635</v>
+        <v>-0.0018</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0674</v>
+        <v>-1.13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6802</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7476</v>
+        <v>-1.13</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5764</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0735</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5028</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5857</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7387</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9907</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3348</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6558</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5721000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0707</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4986</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1507</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3459</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.13</v>
+        <v>-2.1722</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.4554</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.13</v>
+        <v>-1.7168</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-1.5764</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.0735</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.5028</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.7387</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.9907</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.3348</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.6558</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.5327</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0649</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.4678</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>-1.1507</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-1.3459</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0355</v>
+        <v>-3.311</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9351</v>
+        <v>-1.488</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1004</v>
+        <v>-1.823</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0509</v>
@@ -1078,13 +1078,13 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6801</v>
+        <v>-0.9556</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3699</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3102</v>
+        <v>-0.0328</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8695</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1948</v>
+        <v>-5.7651</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4838</v>
+        <v>-5.9308</v>
       </c>
       <c r="F9" t="n">
-        <v>0.289</v>
+        <v>0.1657</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0435</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5463</v>
+        <v>-0.024</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0769</v>
+        <v>-0.5239</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6232</v>
+        <v>0.4999</v>
       </c>
       <c r="V9" t="n">
         <v>0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8106</v>
+        <v>-6.112</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4431</v>
+        <v>-5.2376</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3676</v>
+        <v>-0.8744</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6872</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4507</v>
+        <v>-1.7521</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7809</v>
+        <v>-1.5754</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6698</v>
+        <v>-0.1767</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.6297</v>
+        <v>-10.2546</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.754099999999999</v>
+        <v>-8.101599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8756</v>
+        <v>-2.153</v>
       </c>
       <c r="G11" t="n">
         <v>-6.5044</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7556</v>
+        <v>-1.3805</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3699</v>
+        <v>-0.7174</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3856</v>
+        <v>-0.663</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4997</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.3484</v>
+        <v>-21.321</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.0564</v>
+        <v>-13.0288</v>
       </c>
       <c r="F12" t="n">
         <v>-8.292199999999999</v>
@@ -1390,13 +1390,13 @@
         <v>13.0504</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.760399999999999</v>
+        <v>-7.732999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.979199999999999</v>
+        <v>-6.951600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7812000000000001</v>
+        <v>-0.7812</v>
       </c>
       <c r="V12" t="n">
         <v>0.5443</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.1927</v>
+        <v>8.622999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2061</v>
+        <v>6.9893</v>
       </c>
       <c r="F13" t="n">
-        <v>4.9866</v>
+        <v>1.6337</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5063</v>
+        <v>5.1298</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1987</v>
+        <v>3.5097</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3076</v>
+        <v>1.62</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3558</v>
+        <v>4.9745</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8609</v>
+        <v>2.4851</v>
       </c>
       <c r="L13" t="n">
-        <v>1.495</v>
+        <v>2.4894</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1504</v>
+        <v>0.1553</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3378</v>
+        <v>1.0247</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1873</v>
+        <v>-0.8694</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8276</v>
+        <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2955</v>
+        <v>0.5357</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2869</v>
+        <v>-0.2451</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0086</v>
+        <v>0.7808</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3491</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3491</v>
+        <v>2.2599</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6866</v>
+        <v>6.474</v>
       </c>
       <c r="E14" t="n">
-        <v>6.207</v>
+        <v>1.6415</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4796</v>
+        <v>4.8325</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1298</v>
+        <v>2.5063</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5097</v>
+        <v>2.1987</v>
       </c>
       <c r="I14" t="n">
-        <v>1.62</v>
+        <v>0.3076</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9745</v>
+        <v>2.3558</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4851</v>
+        <v>0.8609</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4894</v>
+        <v>1.495</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1553</v>
+        <v>0.1504</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0247</v>
+        <v>1.3378</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8694</v>
+        <v>-1.1873</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>2.8276</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4008</v>
+        <v>2.5767</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0274</v>
+        <v>0.7222</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6267</v>
+        <v>1.8545</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3491</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2599</v>
+        <v>-0.3491</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2333</v>
+        <v>4.5492</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0394</v>
+        <v>2.9681</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2727</v>
+        <v>1.5812</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4192</v>
+        <v>3.4712</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0376</v>
+        <v>3.0321</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6183</v>
+        <v>0.4391</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9484</v>
+        <v>2.6664</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0799</v>
+        <v>1.8249</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1314</v>
+        <v>0.8415</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4708</v>
+        <v>0.8047</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9577</v>
+        <v>1.2072</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4869</v>
+        <v>-0.4024</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8276</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>3.249</v>
+        <v>1.1629</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8843</v>
+        <v>0.3016</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3648</v>
+        <v>0.8613</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3904</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9481</v>
+        <v>3.2686</v>
       </c>
       <c r="E16" t="n">
-        <v>2.521</v>
+        <v>-0.4049</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4271</v>
+        <v>3.6735</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4712</v>
+        <v>1.7941</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0321</v>
+        <v>-1.183</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4391</v>
+        <v>2.9771</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6664</v>
+        <v>1.8882</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8249</v>
+        <v>-1.9583</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8415</v>
+        <v>3.8465</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8047</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2072</v>
+        <v>0.7752</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4024</v>
+        <v>-0.8694</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1751</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-5.4377</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>2.8276</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5618</v>
+        <v>1.455</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1454</v>
+        <v>0.3197</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7072000000000001</v>
+        <v>1.1353</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.2599</v>
+        <v>2.6297</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.8249</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2599</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5673</v>
+        <v>3.135</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0754</v>
+        <v>-1.0453</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6427</v>
+        <v>4.1802</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7941</v>
+        <v>1.4192</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.183</v>
+        <v>2.0376</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9771</v>
+        <v>-0.6183</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8882</v>
+        <v>0.9484</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.9583</v>
+        <v>1.0799</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8465</v>
+        <v>-0.1314</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.4708</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7752</v>
+        <v>0.9577</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8694</v>
+        <v>-0.4869</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.6101</v>
+        <v>-0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.4377</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
         <v>2.8276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7536</v>
+        <v>2.1507</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3509</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1045</v>
+        <v>1.2723</v>
       </c>
       <c r="V17" t="n">
-        <v>2.6297</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8249</v>
+        <v>0.3904</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3002</v>
+        <v>2.5353</v>
       </c>
       <c r="E18" t="n">
-        <v>0.394</v>
+        <v>0.5057</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9062</v>
+        <v>2.0295</v>
       </c>
       <c r="G18" t="n">
         <v>1.1598</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5977</v>
+        <v>0.8328</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2139</v>
+        <v>-0.1021</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8116</v>
+        <v>0.9349</v>
       </c>
       <c r="V18" t="n">
         <v>0.7602</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8445</v>
+        <v>1.4148</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.248</v>
+        <v>0.199</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0925</v>
+        <v>1.2158</v>
       </c>
       <c r="G19" t="n">
         <v>0.0533</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2963</v>
+        <v>0.274</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0959</v>
+        <v>-0.6489</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7996</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9786</v>
+        <v>-1.1927</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5531</v>
+        <v>0.4792</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4255</v>
+        <v>-1.6719</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3196</v>
+        <v>-0.6712</v>
       </c>
       <c r="H20" t="n">
-        <v>1.028</v>
+        <v>1.034</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7084</v>
+        <v>-1.7053</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7914</v>
+        <v>0.4612</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7149</v>
+        <v>1.168</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0765</v>
+        <v>-0.7068</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4718</v>
+        <v>-1.1324</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3131</v>
+        <v>-0.1339</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7849</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4419</v>
+        <v>-0.3263</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2656</v>
+        <v>0.018</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1763</v>
+        <v>-0.3443</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4779</v>
+        <v>-2.0729</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2557</v>
+        <v>-1.0001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7336</v>
+        <v>-1.0728</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6712</v>
+        <v>0.3196</v>
       </c>
       <c r="H21" t="n">
-        <v>1.034</v>
+        <v>1.028</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7053</v>
+        <v>-0.7084</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4612</v>
+        <v>0.7914</v>
       </c>
       <c r="K21" t="n">
-        <v>1.168</v>
+        <v>0.7149</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7068</v>
+        <v>0.0765</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1324</v>
+        <v>-0.4718</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1339</v>
+        <v>0.3131</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.7849</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.3476</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2055</v>
+        <v>-0.1815</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4059</v>
+        <v>0.529</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9678</v>
+        <v>-4.3859</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5709</v>
+        <v>-2.2356</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3969</v>
+        <v>-2.1503</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2247</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8306</v>
+        <v>-0.2488</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2141</v>
+        <v>0.0324</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2206,7 +2206,7 @@
         <v>22.3484</v>
       </c>
       <c r="E23" t="n">
-        <v>8.097</v>
+        <v>8.096900000000002</v>
       </c>
       <c r="F23" t="n">
         <v>14.2514</v>
@@ -2224,10 +2224,10 @@
         <v>13.7194</v>
       </c>
       <c r="K23" t="n">
-        <v>5.2486</v>
+        <v>5.248600000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>8.4709</v>
+        <v>8.470899999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-1.7623</v>
@@ -2248,16 +2248,16 @@
         <v>15.2255</v>
       </c>
       <c r="S23" t="n">
-        <v>8.760400000000001</v>
+        <v>8.760300000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7813000000000001</v>
+        <v>0.7811999999999998</v>
       </c>
       <c r="U23" t="n">
-        <v>7.979299999999999</v>
+        <v>7.9791</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5443</v>
+        <v>-0.5442999999999998</v>
       </c>
       <c r="W23" t="n">
         <v>6.6465</v>
